--- a/edits_list.xlsx
+++ b/edits_list.xlsx
@@ -1,152 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishnu\Cursor_AI_proj\GIT_HUB\headers\renaming_files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_CB1BDC78DF0A169CF2C65BE0482F320875111012" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="WGS_CSBD" sheetId="1" r:id="rId1"/>
-    <sheet name="GBDF" sheetId="2" r:id="rId2"/>
-    <sheet name="KERNAL" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_list" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">GBDF!$A$1:$I$2</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
-  <si>
-    <t>List of Edits that need to be Automated</t>
-  </si>
-  <si>
-    <t>Test Sutie ID</t>
-  </si>
-  <si>
-    <t>Postman Collection</t>
-  </si>
-  <si>
-    <t>Link to postman Collection for smoke</t>
-  </si>
-  <si>
-    <t>Link to postman Collection for regression</t>
-  </si>
-  <si>
-    <t>Refbd Dependency</t>
-  </si>
-  <si>
-    <t>Assignee</t>
-  </si>
-  <si>
-    <t>Cmd status</t>
-  </si>
-  <si>
-    <t>generate_command</t>
-  </si>
-  <si>
-    <t>0001~sample_model~dummy~004</t>
-  </si>
-  <si>
-    <t>TS_1</t>
-  </si>
-  <si>
-    <t>Created</t>
-  </si>
-  <si>
-    <t>Note:
-Sample:
-RULEEM000001~covid~wgs~csbd~00W04--live : python main_processor.py --wgs_csbd --CSBDTS01</t>
-  </si>
-  <si>
-    <t>List of Edits  to be Automated</t>
-  </si>
-  <si>
-    <t>000001~sample model~qwer~abc~v</t>
-  </si>
-  <si>
-    <t>TS_46</t>
-  </si>
-  <si>
-    <t>TS_46_Covid_GBD_MCR_v04_Smoke.json</t>
-  </si>
-  <si>
-    <t>TS_46_Covid_GBD_MCR_v04_Regression.json</t>
-  </si>
-  <si>
-    <t>Anupama</t>
-  </si>
-  <si>
-    <t>sample~asdf~00</t>
-  </si>
-  <si>
-    <t>TS_76</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -182,58 +89,96 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -521,210 +466,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1048480"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="97" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43" bestFit="1" customWidth="1"/>
+    <col width="97" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="17.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="32.77734375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="35.88671875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="17.21875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="8.33203125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="43" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>List of Edits that need to be Automated</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Sutie ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Postman Collection</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link to postman Collection for smoke</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link to postman Collection for regression</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Refbd Dependency</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Assignee</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cmd status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>generate_command</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="H2" t="s">
-        <v>11</v>
+    <row r="2" ht="15.6" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>00001~sample_model~cba~dfg~m1~001--live</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>TS_1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>TS_1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>python main_processor.py --model_1 --TS01</t>
+        </is>
       </c>
     </row>
-    <row r="1048480" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1048480" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="81.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="126.21875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="44.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>B2</f>
-        <v>TS_46</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="88.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="str">
-        <f>B2</f>
-        <v>TS_76</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="H2" s="2"/>
+    <row r="1048480">
+      <c r="A1048480" t="inlineStr">
+        <is>
+          <t>Note:
+Sample:
+RULEEM000001~covid~wgs~csbd~00W04--live : python main_processor.py --wgs_csbd --CSBDTS01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
